--- a/Figure 6/Figure 6-K.xlsx
+++ b/Figure 6/Figure 6-K.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\图6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\iMetaOmics7798648\Figure 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D10DBA-0CC4-43F1-9EF6-6F138BDECFD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6705BD6-A81B-4F43-BCC6-3D644E58BFDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23800" yWindow="3060" windowWidth="19500" windowHeight="15580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-1540" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>IL-10(ng/L)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -60,10 +60,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CON 6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ETEC 1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -108,10 +104,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ETEC+WB800 6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ETEC+WB800_KR32 1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -129,10 +121,6 @@
   </si>
   <si>
     <t>ETEC+WB800_KR32 5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ETEC+WB800_KR32 6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -143,7 +131,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -159,24 +147,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -199,23 +178,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -498,201 +471,184 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" customWidth="1"/>
-    <col min="2" max="2" width="12.08203125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12.08203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="2"/>
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="3">
         <v>136.54509999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="3" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2"/>
-    </row>
-    <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B3" s="3">
+        <v>133.57740000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1">
-        <v>133.57740000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B4" s="3">
+        <v>157.7372</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="1">
-        <v>157.7372</v>
+      <c r="B5" s="4">
+        <v>148.03980000000001</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
-        <v>148.03980000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B6" s="4">
+        <v>136.12710000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>136.12710000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+        <v>117.35939999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="1">
-        <v>117.35939999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="B8" s="3">
+        <v>92.572699999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="1">
-        <v>92.572699999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="B9" s="3">
+        <v>111.9256</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="1">
-        <v>111.9256</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="B10" s="3">
+        <v>107.20229999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="1">
-        <v>107.20229999999999</v>
+      <c r="B11" s="4">
+        <v>98.717100000000002</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="3">
-        <v>98.717100000000002</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="B12" s="4">
+        <v>114.80970000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>114.80970000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+        <v>122.0827</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="1">
-        <v>122.0827</v>
+      <c r="B14" s="4">
+        <v>125.55200000000001</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="3">
-        <v>125.55200000000001</v>
+      <c r="B15" s="4">
+        <v>139.9727</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="3">
-        <v>139.9727</v>
+      <c r="B16" s="4">
+        <v>131.94730000000001</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="3">
-        <v>131.94730000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="B17" s="4">
+        <v>132.32339999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="4"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="B18" s="3">
+        <v>152.47049999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>132.32339999999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+        <v>139.72190000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="1">
-        <v>152.47049999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="B20" s="3">
+        <v>154.4769</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="1">
-        <v>139.72190000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="B21" s="4">
+        <v>143.9435</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="2"/>
-    </row>
-    <row r="23" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="1">
-        <v>154.4769</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" s="3">
-        <v>143.9435</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" s="3">
+      <c r="B22" s="4">
         <v>137.8827</v>
       </c>
     </row>
